--- a/data/bench/benchmark_report.xlsx
+++ b/data/bench/benchmark_report.xlsx
@@ -13,8 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Colors" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DPS Builds'!$A$1:$G$104</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ALAC Builds'!$A$1:$G$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DPS Builds'!$A$1:$G$107</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ALAC Builds'!$A$1:$G$44</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'QUICK Builds'!$A$1:$G$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H104"/>
+  <dimension ref="A1:H107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="13" customWidth="1" min="8" max="8"/>
@@ -618,19 +618,19 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Power Daredevil Dagger Dagger Axe Pistol</t>
+          <t>Condition Antiquary Scepter Dagger</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>condition</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>44282</v>
+        <v>44370</v>
       </c>
       <c r="E4">
         <f>ROUND(C4/D4*100,2)</f>
@@ -653,7 +653,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Power Daredevil Dagger Only</t>
+          <t>Power Daredevil Dagger Dagger Axe Pistol</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -688,7 +688,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Power Antiquary Staff Dagger Pistol</t>
+          <t>Power Daredevil Dagger Only</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -700,7 +700,7 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>44271</v>
+        <v>44282</v>
       </c>
       <c r="E6">
         <f>ROUND(C6/D6*100,2)</f>
@@ -721,9 +721,9 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>Power Berserker Axe Axe Sword Mace</t>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Power Antiquary Staff Dagger Pistol</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -735,7 +735,7 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>44256</v>
+        <v>44271</v>
       </c>
       <c r="E7">
         <f>ROUND(C7/D7*100,2)</f>
@@ -751,14 +751,14 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>warrior</t>
+          <t>thief</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Power Antiquary Spear Axe Pistol</t>
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Power Berserker Axe Axe Sword Mace</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,7 +770,7 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>44233</v>
+        <v>44256</v>
       </c>
       <c r="E8">
         <f>ROUND(C8/D8*100,2)</f>
@@ -786,26 +786,26 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>thief</t>
+          <t>warrior</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Condition Mirage Ih Oasis Staff Axe Torch</t>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Power Antiquary Spear Axe Pistol</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>condition</t>
+          <t>power</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>44170</v>
+        <v>44233</v>
       </c>
       <c r="E9">
         <f>ROUND(C9/D9*100,2)</f>
@@ -821,14 +821,14 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>mesmer</t>
+          <t>thief</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Condition Berserker Longbow Sword Torch</t>
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Condition Mirage Ih Oasis Staff Axe Torch</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -840,7 +840,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>44151</v>
+        <v>44170</v>
       </c>
       <c r="E10">
         <f>ROUND(C10/D10*100,2)</f>
@@ -856,14 +856,14 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>warrior</t>
+          <t>mesmer</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>Condition Evoker Specialized Elements</t>
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Condition Berserker Longbow Sword Torch</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -875,7 +875,7 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>44135</v>
+        <v>44151</v>
       </c>
       <c r="E11">
         <f>ROUND(C11/D11*100,2)</f>
@@ -891,14 +891,14 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>elementalist</t>
+          <t>warrior</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Condition Weaver Pistol Dagger</t>
+          <t>Condition Evoker Specialized Elements</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -910,7 +910,7 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>43829</v>
+        <v>44135</v>
       </c>
       <c r="E12">
         <f>ROUND(C12/D12*100,2)</f>
@@ -931,9 +931,9 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Condition Mirage Ih Ether Staff Axe Torch</t>
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Condition Weaver Pistol Dagger</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -945,7 +945,7 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>43608</v>
+        <v>43829</v>
       </c>
       <c r="E13">
         <f>ROUND(C13/D13*100,2)</f>
@@ -961,26 +961,26 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>mesmer</t>
+          <t>elementalist</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>Power Amalgam Double Helix Hammer</t>
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Condition Mirage Ih Ether Staff Axe Torch</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>condition</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>43571</v>
+        <v>43608</v>
       </c>
       <c r="E14">
         <f>ROUND(C14/D14*100,2)</f>
@@ -996,26 +996,26 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>engineer</t>
+          <t>mesmer</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>Condition Reaper Spear Dagger Sword</t>
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Power Amalgam Double Helix Hammer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>condition</t>
+          <t>power</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>43537</v>
+        <v>43571</v>
       </c>
       <c r="E15">
         <f>ROUND(C15/D15*100,2)</f>
@@ -1031,14 +1031,14 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>necromancer</t>
+          <t>engineer</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>Condition Amalgam Three Kits Spear</t>
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>Condition Reaper Spear Dagger Sword</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1050,7 +1050,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>43533</v>
+        <v>43537</v>
       </c>
       <c r="E16">
         <f>ROUND(C16/D16*100,2)</f>
@@ -1066,14 +1066,14 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>engineer</t>
+          <t>necromancer</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Condition Antiquary Scepter Dagger</t>
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Condition Amalgam Three Kits Spear</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1085,7 +1085,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>43451</v>
+        <v>43533</v>
       </c>
       <c r="E17">
         <f>ROUND(C17/D17*100,2)</f>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>thief</t>
+          <t>engineer</t>
         </is>
       </c>
     </row>
@@ -1351,9 +1351,9 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>Condition Weaver Pistol Warhorn</t>
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Condition Mirage Dune Cloak Staff Axe Torch</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1381,26 +1381,26 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>elementalist</t>
+          <t>mesmer</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>Power Untamed Beastmastery Hammer Sword Axe</t>
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Condition Weaver Pistol Warhorn</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>condition</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>42705</v>
+        <v>42706</v>
       </c>
       <c r="E26">
         <f>ROUND(C26/D26*100,2)</f>
@@ -1416,14 +1416,14 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>ranger</t>
+          <t>elementalist</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="10" t="inlineStr">
-        <is>
-          <t>Power Vindicator Greatsword Sword Sword</t>
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Power Untamed Beastmastery Hammer Sword Axe</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1435,7 +1435,7 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>42670</v>
+        <v>42705</v>
       </c>
       <c r="E27">
         <f>ROUND(C27/D27*100,2)</f>
@@ -1451,26 +1451,26 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>revenant</t>
+          <t>ranger</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>Condition Evoker Pistol Dagger</t>
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>Power Vindicator Greatsword Sword Sword</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>condition</t>
+          <t>power</t>
         </is>
       </c>
       <c r="C28" t="n">
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>42665</v>
+        <v>42670</v>
       </c>
       <c r="E28">
         <f>ROUND(C28/D28*100,2)</f>
@@ -1486,14 +1486,14 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>elementalist</t>
+          <t>revenant</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>Condition Chronomancer Staff Scepter Torch</t>
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Condition Evoker Pistol Dagger</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1505,7 +1505,7 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>42653</v>
+        <v>42665</v>
       </c>
       <c r="E29">
         <f>ROUND(C29/D29*100,2)</f>
@@ -1521,26 +1521,26 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>mesmer</t>
+          <t>elementalist</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>Power Spellbreaker Dagger Mace Dagger Axe</t>
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Condition Chronomancer Staff Scepter Torch</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>condition</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>42633</v>
+        <v>42653</v>
       </c>
       <c r="E30">
         <f>ROUND(C30/D30*100,2)</f>
@@ -1556,14 +1556,14 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>warrior</t>
+          <t>mesmer</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>Power Galeshot Longbow Axe Axe</t>
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Power Spellbreaker Dagger Mace Dagger Axe</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1575,7 +1575,7 @@
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>42575</v>
+        <v>42633</v>
       </c>
       <c r="E31">
         <f>ROUND(C31/D31*100,2)</f>
@@ -1591,26 +1591,26 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>ranger</t>
+          <t>warrior</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>Condition Soulbeast Shortbow Dagger Dagger</t>
+          <t>Power Galeshot Longbow Axe Axe</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>condition</t>
+          <t>power</t>
         </is>
       </c>
       <c r="C32" t="n">
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>42481</v>
+        <v>42575</v>
       </c>
       <c r="E32">
         <f>ROUND(C32/D32*100,2)</f>
@@ -1631,9 +1631,9 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>Power Bladesworn Faf Sword Pistol</t>
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Power Troubadour Spear Dagger Sword</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1645,7 +1645,7 @@
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>42457</v>
+        <v>42507</v>
       </c>
       <c r="E33">
         <f>ROUND(C33/D33*100,2)</f>
@@ -1661,26 +1661,26 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>warrior</t>
+          <t>mesmer</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>Power Berserker Whirlpain Spear Greatsword</t>
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Condition Soulbeast Shortbow Dagger Dagger</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>condition</t>
         </is>
       </c>
       <c r="C34" t="n">
         <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>42362</v>
+        <v>42481</v>
       </c>
       <c r="E34">
         <f>ROUND(C34/D34*100,2)</f>
@@ -1696,14 +1696,14 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>warrior</t>
+          <t>ranger</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="10" t="inlineStr">
-        <is>
-          <t>Power Renegade Greatsword Sword Sword</t>
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Power Bladesworn Faf Sword Pistol</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1715,7 +1715,7 @@
         <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>42297</v>
+        <v>42457</v>
       </c>
       <c r="E35">
         <f>ROUND(C35/D35*100,2)</f>
@@ -1731,26 +1731,26 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>revenant</t>
+          <t>warrior</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="8" t="inlineStr">
-        <is>
-          <t>Condition Harbinger Pistol Torch Scepter Dagger</t>
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Power Berserker Whirlpain Spear Greatsword</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>condition</t>
+          <t>power</t>
         </is>
       </c>
       <c r="C36" t="n">
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>42276</v>
+        <v>42362</v>
       </c>
       <c r="E36">
         <f>ROUND(C36/D36*100,2)</f>
@@ -1766,26 +1766,26 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>necromancer</t>
+          <t>warrior</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="11" t="inlineStr">
-        <is>
-          <t>Condition Willbender Pistol Torch Pistol</t>
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>Power Renegade Greatsword Sword Sword</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>condition</t>
+          <t>power</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>42265</v>
+        <v>42297</v>
       </c>
       <c r="E37">
         <f>ROUND(C37/D37*100,2)</f>
@@ -1801,26 +1801,26 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>guardian</t>
+          <t>revenant</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>Power Virtuoso Spear Greatsword</t>
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>Condition Harbinger Pistol Torch Scepter Dagger</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>condition</t>
         </is>
       </c>
       <c r="C38" t="n">
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>42218</v>
+        <v>42276</v>
       </c>
       <c r="E38">
         <f>ROUND(C38/D38*100,2)</f>
@@ -1836,26 +1836,26 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>mesmer</t>
+          <t>necromancer</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="7" t="inlineStr">
-        <is>
-          <t>Power Scrapper Hammer</t>
+      <c r="A39" s="11" t="inlineStr">
+        <is>
+          <t>Condition Willbender Pistol Torch Pistol</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>condition</t>
         </is>
       </c>
       <c r="C39" t="n">
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>42205</v>
+        <v>42265</v>
       </c>
       <c r="E39">
         <f>ROUND(C39/D39*100,2)</f>
@@ -1871,14 +1871,14 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>engineer</t>
+          <t>guardian</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>Power Paragon Sword Axe Dagger Mace</t>
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>Power Virtuoso Spear Greatsword</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1890,7 +1890,7 @@
         <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>42187</v>
+        <v>42218</v>
       </c>
       <c r="E40">
         <f>ROUND(C40/D40*100,2)</f>
@@ -1906,14 +1906,14 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>warrior</t>
+          <t>mesmer</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="11" t="inlineStr">
-        <is>
-          <t>Power Dragonhunter Radiance Longbow Greatsword</t>
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>Power Scrapper Hammer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1925,7 +1925,7 @@
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>42179</v>
+        <v>42205</v>
       </c>
       <c r="E41">
         <f>ROUND(C41/D41*100,2)</f>
@@ -1941,14 +1941,14 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>guardian</t>
+          <t>engineer</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="7" t="inlineStr">
-        <is>
-          <t>Power Amalgam Hammer</t>
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Power Paragon Sword Axe Dagger Mace</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1960,7 +1960,7 @@
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>42170</v>
+        <v>42187</v>
       </c>
       <c r="E42">
         <f>ROUND(C42/D42*100,2)</f>
@@ -1976,26 +1976,26 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>engineer</t>
+          <t>warrior</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>Condition Thief Axe Dagger Only</t>
+      <c r="A43" s="11" t="inlineStr">
+        <is>
+          <t>Power Dragonhunter Radiance Longbow Greatsword</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>condition</t>
+          <t>power</t>
         </is>
       </c>
       <c r="C43" t="n">
         <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>42108</v>
+        <v>42179</v>
       </c>
       <c r="E43">
         <f>ROUND(C43/D43*100,2)</f>
@@ -2011,26 +2011,26 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>thief</t>
+          <t>guardian</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>Condition Mechanist Two Kits Spear</t>
+          <t>Power Amalgam Hammer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>condition</t>
+          <t>power</t>
         </is>
       </c>
       <c r="C44" t="n">
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>42018</v>
+        <v>42170</v>
       </c>
       <c r="E44">
         <f>ROUND(C44/D44*100,2)</f>
@@ -2051,21 +2051,21 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="6" t="inlineStr">
-        <is>
-          <t>Power Catalyst Scepter Dagger</t>
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Condition Thief Axe Dagger Only</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>condition</t>
         </is>
       </c>
       <c r="C45" t="n">
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>42006</v>
+        <v>42108</v>
       </c>
       <c r="E45">
         <f>ROUND(C45/D45*100,2)</f>
@@ -2081,26 +2081,26 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>elementalist</t>
+          <t>thief</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>Power Holosmith Sword Pistol</t>
+          <t>Condition Mechanist Two Kits Spear</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>condition</t>
         </is>
       </c>
       <c r="C46" t="n">
         <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>41981</v>
+        <v>42018</v>
       </c>
       <c r="E46">
         <f>ROUND(C46/D46*100,2)</f>
@@ -2121,21 +2121,21 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="10" t="inlineStr">
-        <is>
-          <t>Condition Renegade Spear Mace Axe</t>
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>Power Catalyst Scepter Dagger</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>condition</t>
+          <t>power</t>
         </is>
       </c>
       <c r="C47" t="n">
         <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>41900</v>
+        <v>42006</v>
       </c>
       <c r="E47">
         <f>ROUND(C47/D47*100,2)</f>
@@ -2151,14 +2151,14 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>revenant</t>
+          <t>elementalist</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="11" t="inlineStr">
-        <is>
-          <t>Power Dragonhunter Radiance Spear Greatsword</t>
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>Power Holosmith Sword Pistol</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2170,7 +2170,7 @@
         <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>41879</v>
+        <v>41981</v>
       </c>
       <c r="E48">
         <f>ROUND(C48/D48*100,2)</f>
@@ -2186,26 +2186,26 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>guardian</t>
+          <t>engineer</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>Power Antiquary Rifle Only</t>
+      <c r="A49" s="10" t="inlineStr">
+        <is>
+          <t>Condition Renegade Spear Mace Axe</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>condition</t>
         </is>
       </c>
       <c r="C49" t="n">
         <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>41818</v>
+        <v>41900</v>
       </c>
       <c r="E49">
         <f>ROUND(C49/D49*100,2)</f>
@@ -2221,26 +2221,26 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>thief</t>
+          <t>revenant</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>Condition Tempest Pistol Warhorn</t>
+      <c r="A50" s="11" t="inlineStr">
+        <is>
+          <t>Power Dragonhunter Radiance Spear Greatsword</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>condition</t>
+          <t>power</t>
         </is>
       </c>
       <c r="C50" t="n">
         <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>41703</v>
+        <v>41879</v>
       </c>
       <c r="E50">
         <f>ROUND(C50/D50*100,2)</f>
@@ -2256,26 +2256,26 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>elementalist</t>
+          <t>guardian</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="9" t="inlineStr">
-        <is>
-          <t>Condition Conduit Spear Mace Axe</t>
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Power Antiquary Rifle Only</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>condition</t>
+          <t>power</t>
         </is>
       </c>
       <c r="C51" t="n">
         <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>41698</v>
+        <v>41818</v>
       </c>
       <c r="E51">
         <f>ROUND(C51/D51*100,2)</f>
@@ -2291,26 +2291,26 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>thief</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="8" t="inlineStr">
-        <is>
-          <t>Power Harbinger Greatsword Spear</t>
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>Condition Tempest Pistol Warhorn</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>condition</t>
         </is>
       </c>
       <c r="C52" t="n">
         <v>0</v>
       </c>
       <c r="D52" t="n">
-        <v>41692</v>
+        <v>41703</v>
       </c>
       <c r="E52">
         <f>ROUND(C52/D52*100,2)</f>
@@ -2326,14 +2326,14 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>necromancer</t>
+          <t>elementalist</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>Condition Daredevil Dagger Only</t>
+      <c r="A53" s="9" t="inlineStr">
+        <is>
+          <t>Condition Conduit Spear Mace Axe</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2345,7 +2345,7 @@
         <v>0</v>
       </c>
       <c r="D53" t="n">
-        <v>41689</v>
+        <v>41698</v>
       </c>
       <c r="E53">
         <f>ROUND(C53/D53*100,2)</f>
@@ -2361,26 +2361,26 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>thief</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>Condition Specter Spear Only</t>
+      <c r="A54" s="8" t="inlineStr">
+        <is>
+          <t>Power Harbinger Greatsword Spear</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>condition</t>
+          <t>power</t>
         </is>
       </c>
       <c r="C54" t="n">
         <v>0</v>
       </c>
       <c r="D54" t="n">
-        <v>41653</v>
+        <v>41692</v>
       </c>
       <c r="E54">
         <f>ROUND(C54/D54*100,2)</f>
@@ -2396,26 +2396,26 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>thief</t>
+          <t>necromancer</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="6" t="inlineStr">
-        <is>
-          <t>Power Evoker Scepter Dagger</t>
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Condition Daredevil Dagger Only</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>condition</t>
         </is>
       </c>
       <c r="C55" t="n">
         <v>0</v>
       </c>
       <c r="D55" t="n">
-        <v>41646</v>
+        <v>41689</v>
       </c>
       <c r="E55">
         <f>ROUND(C55/D55*100,2)</f>
@@ -2431,14 +2431,14 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>elementalist</t>
+          <t>thief</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="11" t="inlineStr">
-        <is>
-          <t>Condition Willbender Scepter Pistol Pistol Torch</t>
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Condition Specter Spear Only</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2450,7 +2450,7 @@
         <v>0</v>
       </c>
       <c r="D56" t="n">
-        <v>41590</v>
+        <v>41653</v>
       </c>
       <c r="E56">
         <f>ROUND(C56/D56*100,2)</f>
@@ -2466,14 +2466,14 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>guardian</t>
+          <t>thief</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="8" t="inlineStr">
-        <is>
-          <t>Power Reaper Greatsword Spear</t>
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>Power Evoker Scepter Dagger</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2485,7 +2485,7 @@
         <v>0</v>
       </c>
       <c r="D57" t="n">
-        <v>41533</v>
+        <v>41646</v>
       </c>
       <c r="E57">
         <f>ROUND(C57/D57*100,2)</f>
@@ -2501,26 +2501,26 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>necromancer</t>
+          <t>elementalist</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="6" t="inlineStr">
-        <is>
-          <t>Power Tempest Spear</t>
+      <c r="A58" s="11" t="inlineStr">
+        <is>
+          <t>Condition Willbender Scepter Pistol Pistol Torch</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>condition</t>
         </is>
       </c>
       <c r="C58" t="n">
         <v>0</v>
       </c>
       <c r="D58" t="n">
-        <v>41514</v>
+        <v>41590</v>
       </c>
       <c r="E58">
         <f>ROUND(C58/D58*100,2)</f>
@@ -2536,14 +2536,14 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>elementalist</t>
+          <t>guardian</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="6" t="inlineStr">
-        <is>
-          <t>Power Tempest Sword Dagger</t>
+      <c r="A59" s="8" t="inlineStr">
+        <is>
+          <t>Power Reaper Greatsword Spear</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2555,7 +2555,7 @@
         <v>0</v>
       </c>
       <c r="D59" t="n">
-        <v>41502</v>
+        <v>41533</v>
       </c>
       <c r="E59">
         <f>ROUND(C59/D59*100,2)</f>
@@ -2571,26 +2571,26 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>elementalist</t>
+          <t>necromancer</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="10" t="inlineStr">
-        <is>
-          <t>Condition Renegade Shortbow Mace Axe</t>
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>Power Tempest Spear</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>condition</t>
+          <t>power</t>
         </is>
       </c>
       <c r="C60" t="n">
         <v>0</v>
       </c>
       <c r="D60" t="n">
-        <v>41500</v>
+        <v>41514</v>
       </c>
       <c r="E60">
         <f>ROUND(C60/D60*100,2)</f>
@@ -2606,14 +2606,14 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>revenant</t>
+          <t>elementalist</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>Power Catalyst Spear</t>
+          <t>Power Tempest Sword Dagger</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2625,7 +2625,7 @@
         <v>0</v>
       </c>
       <c r="D61" t="n">
-        <v>41454</v>
+        <v>41502</v>
       </c>
       <c r="E61">
         <f>ROUND(C61/D61*100,2)</f>
@@ -2646,21 +2646,21 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="4" t="inlineStr">
-        <is>
-          <t>Power Berserker Hammer Axe Mace</t>
+      <c r="A62" s="10" t="inlineStr">
+        <is>
+          <t>Condition Renegade Shortbow Mace Axe</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>condition</t>
         </is>
       </c>
       <c r="C62" t="n">
         <v>0</v>
       </c>
       <c r="D62" t="n">
-        <v>41418</v>
+        <v>41500</v>
       </c>
       <c r="E62">
         <f>ROUND(C62/D62*100,2)</f>
@@ -2676,14 +2676,14 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>warrior</t>
+          <t>revenant</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>Power Daredevil Sword Dagger Axe Pistol</t>
+      <c r="A63" s="11" t="inlineStr">
+        <is>
+          <t>Power Luminary Spear Greatsword</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2695,7 +2695,7 @@
         <v>0</v>
       </c>
       <c r="D63" t="n">
-        <v>41321</v>
+        <v>41468</v>
       </c>
       <c r="E63">
         <f>ROUND(C63/D63*100,2)</f>
@@ -2711,14 +2711,14 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>thief</t>
+          <t>guardian</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>Power Tempest Scepter Dagger</t>
+          <t>Power Catalyst Spear</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2730,7 +2730,7 @@
         <v>0</v>
       </c>
       <c r="D64" t="n">
-        <v>41321</v>
+        <v>41454</v>
       </c>
       <c r="E64">
         <f>ROUND(C64/D64*100,2)</f>
@@ -2753,7 +2753,7 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>Power Berserker Tactics Spear Greatsword</t>
+          <t>Power Berserker Hammer Axe Mace</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2765,7 +2765,7 @@
         <v>0</v>
       </c>
       <c r="D65" t="n">
-        <v>41315</v>
+        <v>41418</v>
       </c>
       <c r="E65">
         <f>ROUND(C65/D65*100,2)</f>
@@ -2788,19 +2788,19 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Condition Daredevil Spear Axe Dagger</t>
+          <t>Power Daredevil Sword Dagger Axe Pistol</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>condition</t>
+          <t>power</t>
         </is>
       </c>
       <c r="C66" t="n">
         <v>0</v>
       </c>
       <c r="D66" t="n">
-        <v>41302</v>
+        <v>41321</v>
       </c>
       <c r="E66">
         <f>ROUND(C66/D66*100,2)</f>
@@ -2821,21 +2821,21 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>Condition Daredevil Spear Only</t>
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>Power Tempest Scepter Dagger</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>condition</t>
+          <t>power</t>
         </is>
       </c>
       <c r="C67" t="n">
         <v>0</v>
       </c>
       <c r="D67" t="n">
-        <v>41302</v>
+        <v>41321</v>
       </c>
       <c r="E67">
         <f>ROUND(C67/D67*100,2)</f>
@@ -2851,14 +2851,14 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>thief</t>
+          <t>elementalist</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="10" t="inlineStr">
-        <is>
-          <t>Power Renegade Hammer Sword Sword</t>
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>Power Berserker Tactics Spear Greatsword</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2870,7 +2870,7 @@
         <v>0</v>
       </c>
       <c r="D68" t="n">
-        <v>41300</v>
+        <v>41315</v>
       </c>
       <c r="E68">
         <f>ROUND(C68/D68*100,2)</f>
@@ -2886,26 +2886,26 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>revenant</t>
+          <t>warrior</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="9" t="inlineStr">
-        <is>
-          <t>Power Conduit Staff Sword Sword</t>
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Condition Daredevil Spear Only</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>condition</t>
         </is>
       </c>
       <c r="C69" t="n">
         <v>0</v>
       </c>
       <c r="D69" t="n">
-        <v>41217</v>
+        <v>41302</v>
       </c>
       <c r="E69">
         <f>ROUND(C69/D69*100,2)</f>
@@ -2921,14 +2921,14 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>thief</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="5" t="inlineStr">
-        <is>
-          <t>Power Troubadour Spear Greatsword</t>
+      <c r="A70" s="10" t="inlineStr">
+        <is>
+          <t>Power Renegade Hammer Sword Sword</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2940,7 +2940,7 @@
         <v>0</v>
       </c>
       <c r="D70" t="n">
-        <v>41144</v>
+        <v>41300</v>
       </c>
       <c r="E70">
         <f>ROUND(C70/D70*100,2)</f>
@@ -2956,26 +2956,26 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>mesmer</t>
+          <t>revenant</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="7" t="inlineStr">
-        <is>
-          <t>Power Mechanist Sword Pistol</t>
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Condition Daredevil Spear Axe Dagger</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>condition</t>
         </is>
       </c>
       <c r="C71" t="n">
         <v>0</v>
       </c>
       <c r="D71" t="n">
-        <v>41141</v>
+        <v>41234</v>
       </c>
       <c r="E71">
         <f>ROUND(C71/D71*100,2)</f>
@@ -2991,26 +2991,26 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>engineer</t>
+          <t>thief</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="6" t="inlineStr">
-        <is>
-          <t>Power Weaver Spear</t>
+      <c r="A72" s="11" t="inlineStr">
+        <is>
+          <t>Condition Firebrand Axe Torch Pistol Pistol</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>condition</t>
         </is>
       </c>
       <c r="C72" t="n">
         <v>0</v>
       </c>
       <c r="D72" t="n">
-        <v>41118</v>
+        <v>41218</v>
       </c>
       <c r="E72">
         <f>ROUND(C72/D72*100,2)</f>
@@ -3026,26 +3026,26 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>elementalist</t>
+          <t>guardian</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="4" t="inlineStr">
-        <is>
-          <t>Condition Paragon Longbow Sword Sword</t>
+      <c r="A73" s="9" t="inlineStr">
+        <is>
+          <t>Power Conduit Staff Sword Sword</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>condition</t>
+          <t>power</t>
         </is>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" t="n">
-        <v>41080</v>
+        <v>41217</v>
       </c>
       <c r="E73">
         <f>ROUND(C73/D73*100,2)</f>
@@ -3061,14 +3061,14 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>warrior</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>Power Daredevil Staff</t>
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>Power Troubadour Spear Greatsword</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3080,7 +3080,7 @@
         <v>0</v>
       </c>
       <c r="D74" t="n">
-        <v>41055</v>
+        <v>41144</v>
       </c>
       <c r="E74">
         <f>ROUND(C74/D74*100,2)</f>
@@ -3096,14 +3096,14 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>thief</t>
+          <t>mesmer</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="11" t="inlineStr">
-        <is>
-          <t>Power Willbender Spear Greatsword</t>
+      <c r="A75" s="7" t="inlineStr">
+        <is>
+          <t>Power Mechanist Sword Pistol</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3115,7 +3115,7 @@
         <v>0</v>
       </c>
       <c r="D75" t="n">
-        <v>41009</v>
+        <v>41141</v>
       </c>
       <c r="E75">
         <f>ROUND(C75/D75*100,2)</f>
@@ -3131,14 +3131,14 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>guardian</t>
+          <t>engineer</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>Inferno Catalyst Scepter Dagger</t>
+          <t>Power Weaver Spear</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3150,7 +3150,7 @@
         <v>0</v>
       </c>
       <c r="D76" t="n">
-        <v>40976</v>
+        <v>41118</v>
       </c>
       <c r="E76">
         <f>ROUND(C76/D76*100,2)</f>
@@ -3171,21 +3171,21 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>Power Deadeye M7 Rifle Dagger Dagger</t>
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>Condition Paragon Longbow Sword Sword</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>condition</t>
         </is>
       </c>
       <c r="C77" t="n">
         <v>0</v>
       </c>
       <c r="D77" t="n">
-        <v>40923</v>
+        <v>41080</v>
       </c>
       <c r="E77">
         <f>ROUND(C77/D77*100,2)</f>
@@ -3201,14 +3201,14 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>thief</t>
+          <t>warrior</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="6" t="inlineStr">
-        <is>
-          <t>Inferno Tempest Scepter Dagger</t>
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Power Daredevil Staff</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3220,7 +3220,7 @@
         <v>0</v>
       </c>
       <c r="D78" t="n">
-        <v>40920</v>
+        <v>41055</v>
       </c>
       <c r="E78">
         <f>ROUND(C78/D78*100,2)</f>
@@ -3236,14 +3236,14 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>elementalist</t>
+          <t>thief</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="6" t="inlineStr">
-        <is>
-          <t>Power Tempest Hammer</t>
+      <c r="A79" s="11" t="inlineStr">
+        <is>
+          <t>Power Willbender Spear Greatsword</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3255,7 +3255,7 @@
         <v>0</v>
       </c>
       <c r="D79" t="n">
-        <v>40791</v>
+        <v>41009</v>
       </c>
       <c r="E79">
         <f>ROUND(C79/D79*100,2)</f>
@@ -3271,14 +3271,14 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>elementalist</t>
+          <t>guardian</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>Power Weaver Sword Dagger</t>
+          <t>Inferno Catalyst Scepter Dagger</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3290,7 +3290,7 @@
         <v>0</v>
       </c>
       <c r="D80" t="n">
-        <v>40782</v>
+        <v>40976</v>
       </c>
       <c r="E80">
         <f>ROUND(C80/D80*100,2)</f>
@@ -3311,9 +3311,9 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="11" t="inlineStr">
-        <is>
-          <t>Power Luminary Longbow Greatsword</t>
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>Power Deadeye M7 Rifle Dagger Dagger</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3325,7 +3325,7 @@
         <v>0</v>
       </c>
       <c r="D81" t="n">
-        <v>40774</v>
+        <v>40923</v>
       </c>
       <c r="E81">
         <f>ROUND(C81/D81*100,2)</f>
@@ -3341,14 +3341,14 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>guardian</t>
+          <t>thief</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="11" t="inlineStr">
-        <is>
-          <t>Power Willbender Peitha Greatsword Sword Focus</t>
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>Inferno Tempest Scepter Dagger</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3360,7 +3360,7 @@
         <v>0</v>
       </c>
       <c r="D82" t="n">
-        <v>40746</v>
+        <v>40920</v>
       </c>
       <c r="E82">
         <f>ROUND(C82/D82*100,2)</f>
@@ -3376,26 +3376,26 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>guardian</t>
+          <t>elementalist</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="7" t="inlineStr">
-        <is>
-          <t>Condition Mechanist One Kit Spear</t>
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>Power Tempest Hammer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>condition</t>
+          <t>power</t>
         </is>
       </c>
       <c r="C83" t="n">
         <v>0</v>
       </c>
       <c r="D83" t="n">
-        <v>40667</v>
+        <v>40791</v>
       </c>
       <c r="E83">
         <f>ROUND(C83/D83*100,2)</f>
@@ -3411,26 +3411,26 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>engineer</t>
+          <t>elementalist</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>Condition Specter Scepter Dagger Only</t>
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>Power Weaver Sword Dagger</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>condition</t>
+          <t>power</t>
         </is>
       </c>
       <c r="C84" t="n">
         <v>0</v>
       </c>
       <c r="D84" t="n">
-        <v>40628</v>
+        <v>40782</v>
       </c>
       <c r="E84">
         <f>ROUND(C84/D84*100,2)</f>
@@ -3446,14 +3446,14 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>thief</t>
+          <t>elementalist</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="11" t="inlineStr">
         <is>
-          <t>Power Luminary Spear Greatsword</t>
+          <t>Power Luminary Longbow Greatsword</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3465,7 +3465,7 @@
         <v>0</v>
       </c>
       <c r="D85" t="n">
-        <v>40557</v>
+        <v>40774</v>
       </c>
       <c r="E85">
         <f>ROUND(C85/D85*100,2)</f>
@@ -3486,21 +3486,21 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="6" t="inlineStr">
-        <is>
-          <t>Condition Tempest Scepter Warhorn</t>
+      <c r="A86" s="11" t="inlineStr">
+        <is>
+          <t>Power Willbender Peitha Greatsword Sword Focus</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>condition</t>
+          <t>power</t>
         </is>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" t="n">
-        <v>40470</v>
+        <v>40746</v>
       </c>
       <c r="E86">
         <f>ROUND(C86/D86*100,2)</f>
@@ -3516,26 +3516,26 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>elementalist</t>
+          <t>guardian</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="8" t="inlineStr">
-        <is>
-          <t>Power Reaper Greatsword Dagger Sword</t>
+      <c r="A87" s="7" t="inlineStr">
+        <is>
+          <t>Condition Mechanist One Kit Spear</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>condition</t>
         </is>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" t="n">
-        <v>40410</v>
+        <v>40667</v>
       </c>
       <c r="E87">
         <f>ROUND(C87/D87*100,2)</f>
@@ -3551,26 +3551,26 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>necromancer</t>
+          <t>engineer</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="8" t="inlineStr">
-        <is>
-          <t>Power Reaper Greatsword Sword Sword</t>
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Condition Specter Scepter Dagger Only</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>condition</t>
         </is>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" t="n">
-        <v>40366</v>
+        <v>40628</v>
       </c>
       <c r="E88">
         <f>ROUND(C88/D88*100,2)</f>
@@ -3586,26 +3586,26 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>necromancer</t>
+          <t>thief</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="6" t="inlineStr">
         <is>
-          <t>Power Catalyst Sword Dagger</t>
+          <t>Condition Tempest Scepter Warhorn</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>condition</t>
         </is>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" t="n">
-        <v>40189</v>
+        <v>40470</v>
       </c>
       <c r="E89">
         <f>ROUND(C89/D89*100,2)</f>
@@ -3628,19 +3628,19 @@
     <row r="90">
       <c r="A90" s="8" t="inlineStr">
         <is>
-          <t>Condition Scourge Scepter Torch Pistol</t>
+          <t>Power Reaper Greatsword Dagger Sword</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>condition</t>
+          <t>power</t>
         </is>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" t="n">
-        <v>40060</v>
+        <v>40410</v>
       </c>
       <c r="E90">
         <f>ROUND(C90/D90*100,2)</f>
@@ -3661,21 +3661,21 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="9" t="inlineStr">
-        <is>
-          <t>Condition Conduit Mistfire Spear Mace Axe</t>
+      <c r="A91" s="8" t="inlineStr">
+        <is>
+          <t>Power Reaper Greatsword Sword Sword</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>condition</t>
+          <t>power</t>
         </is>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" t="n">
-        <v>39982</v>
+        <v>40366</v>
       </c>
       <c r="E91">
         <f>ROUND(C91/D91*100,2)</f>
@@ -3691,14 +3691,14 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>necromancer</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="3" t="inlineStr">
-        <is>
-          <t>Power Soulbeast Hammer Axe Axe</t>
+      <c r="A92" s="6" t="inlineStr">
+        <is>
+          <t>Power Catalyst Sword Dagger</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3710,7 +3710,7 @@
         <v>0</v>
       </c>
       <c r="D92" t="n">
-        <v>39871</v>
+        <v>40189</v>
       </c>
       <c r="E92">
         <f>ROUND(C92/D92*100,2)</f>
@@ -3726,26 +3726,26 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>ranger</t>
+          <t>elementalist</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="3" t="inlineStr">
-        <is>
-          <t>Power Soulbeast Hammer Sword Axe</t>
+      <c r="A93" s="8" t="inlineStr">
+        <is>
+          <t>Condition Scourge Scepter Torch Pistol</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>condition</t>
         </is>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" t="n">
-        <v>39858</v>
+        <v>40060</v>
       </c>
       <c r="E93">
         <f>ROUND(C93/D93*100,2)</f>
@@ -3761,26 +3761,26 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>ranger</t>
+          <t>necromancer</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="5" t="inlineStr">
-        <is>
-          <t>Power Virtuoso Greatsword Dagger Sword</t>
+      <c r="A94" s="9" t="inlineStr">
+        <is>
+          <t>Condition Conduit Mistfire Spear Mace Axe</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>condition</t>
         </is>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" t="n">
-        <v>39813</v>
+        <v>39982</v>
       </c>
       <c r="E94">
         <f>ROUND(C94/D94*100,2)</f>
@@ -3796,14 +3796,14 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>mesmer</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="4" t="inlineStr">
-        <is>
-          <t>Power Spellbreaker Hammer Dagger Mace</t>
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t>Power Soulbeast Hammer Axe Axe</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3815,7 +3815,7 @@
         <v>0</v>
       </c>
       <c r="D95" t="n">
-        <v>39709</v>
+        <v>39871</v>
       </c>
       <c r="E95">
         <f>ROUND(C95/D95*100,2)</f>
@@ -3831,26 +3831,26 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>warrior</t>
+          <t>ranger</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="10" t="inlineStr">
-        <is>
-          <t>Condition Renegade Spear Only</t>
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>Power Soulbeast Hammer Sword Axe</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>condition</t>
+          <t>power</t>
         </is>
       </c>
       <c r="C96" t="n">
         <v>0</v>
       </c>
       <c r="D96" t="n">
-        <v>39480</v>
+        <v>39858</v>
       </c>
       <c r="E96">
         <f>ROUND(C96/D96*100,2)</f>
@@ -3866,14 +3866,14 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>revenant</t>
+          <t>ranger</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>Power Virtuoso Spear Dagger Sword</t>
+          <t>Power Virtuoso Greatsword Dagger Sword</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3885,7 +3885,7 @@
         <v>0</v>
       </c>
       <c r="D97" t="n">
-        <v>39346</v>
+        <v>39813</v>
       </c>
       <c r="E97">
         <f>ROUND(C97/D97*100,2)</f>
@@ -3906,21 +3906,21 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="5" t="inlineStr">
-        <is>
-          <t>Condition Virtuoso Dagger Sword Focus</t>
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t>Power Spellbreaker Hammer Dagger Mace</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>condition</t>
+          <t>power</t>
         </is>
       </c>
       <c r="C98" t="n">
         <v>0</v>
       </c>
       <c r="D98" t="n">
-        <v>39115</v>
+        <v>39709</v>
       </c>
       <c r="E98">
         <f>ROUND(C98/D98*100,2)</f>
@@ -3936,14 +3936,14 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>mesmer</t>
+          <t>warrior</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="6" t="inlineStr">
-        <is>
-          <t>Condition Catalyst Pistol Dagger</t>
+      <c r="A99" s="10" t="inlineStr">
+        <is>
+          <t>Condition Renegade Spear Only</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3955,7 +3955,7 @@
         <v>0</v>
       </c>
       <c r="D99" t="n">
-        <v>38625</v>
+        <v>39480</v>
       </c>
       <c r="E99">
         <f>ROUND(C99/D99*100,2)</f>
@@ -3971,14 +3971,14 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>elementalist</t>
+          <t>revenant</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="7" t="inlineStr">
-        <is>
-          <t>Power Mechanist Rifle</t>
+      <c r="A100" s="5" t="inlineStr">
+        <is>
+          <t>Power Virtuoso Spear Dagger Sword</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3990,7 +3990,7 @@
         <v>0</v>
       </c>
       <c r="D100" t="n">
-        <v>38473</v>
+        <v>39346</v>
       </c>
       <c r="E100">
         <f>ROUND(C100/D100*100,2)</f>
@@ -4006,14 +4006,14 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>engineer</t>
+          <t>mesmer</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="7" t="inlineStr">
-        <is>
-          <t>Condition Mechanist No Kit Spear</t>
+      <c r="A101" s="5" t="inlineStr">
+        <is>
+          <t>Condition Virtuoso Dagger Sword Focus</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4025,7 +4025,7 @@
         <v>0</v>
       </c>
       <c r="D101" t="n">
-        <v>38365</v>
+        <v>39115</v>
       </c>
       <c r="E101">
         <f>ROUND(C101/D101*100,2)</f>
@@ -4041,26 +4041,26 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>engineer</t>
+          <t>mesmer</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="4" t="inlineStr">
-        <is>
-          <t>Power Warrior Mace Axe Dagger Mace</t>
+      <c r="A102" s="6" t="inlineStr">
+        <is>
+          <t>Condition Catalyst Pistol Dagger</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>condition</t>
         </is>
       </c>
       <c r="C102" t="n">
         <v>0</v>
       </c>
       <c r="D102" t="n">
-        <v>37398</v>
+        <v>38625</v>
       </c>
       <c r="E102">
         <f>ROUND(C102/D102*100,2)</f>
@@ -4076,14 +4076,14 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>warrior</t>
+          <t>elementalist</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="10" t="inlineStr">
-        <is>
-          <t>Power Herald Staff Sword Sword</t>
+      <c r="A103" s="7" t="inlineStr">
+        <is>
+          <t>Power Mechanist Rifle</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4095,7 +4095,7 @@
         <v>0</v>
       </c>
       <c r="D103" t="n">
-        <v>36921</v>
+        <v>38473</v>
       </c>
       <c r="E103">
         <f>ROUND(C103/D103*100,2)</f>
@@ -4111,14 +4111,14 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>revenant</t>
+          <t>engineer</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="6" t="inlineStr">
-        <is>
-          <t>Condition Quickness Evoker Specialized Elements</t>
+      <c r="A104" s="7" t="inlineStr">
+        <is>
+          <t>Condition Mechanist No Kit Spear</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4130,7 +4130,7 @@
         <v>0</v>
       </c>
       <c r="D104" t="n">
-        <v>0</v>
+        <v>38365</v>
       </c>
       <c r="E104">
         <f>ROUND(C104/D104*100,2)</f>
@@ -4146,12 +4146,117 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
+          <t>engineer</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="4" t="inlineStr">
+        <is>
+          <t>Power Warrior Mace Axe Dagger Mace</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>power</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>0</v>
+      </c>
+      <c r="D105" t="n">
+        <v>37398</v>
+      </c>
+      <c r="E105">
+        <f>ROUND(C105/D105*100,2)</f>
+        <v/>
+      </c>
+      <c r="F105">
+        <f>ROUND(D105*0.95,0)</f>
+        <v/>
+      </c>
+      <c r="G105">
+        <f>ROUND(F105-C105,0)</f>
+        <v/>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>warrior</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="10" t="inlineStr">
+        <is>
+          <t>Power Herald Staff Sword Sword</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>power</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>0</v>
+      </c>
+      <c r="D106" t="n">
+        <v>36921</v>
+      </c>
+      <c r="E106">
+        <f>ROUND(C106/D106*100,2)</f>
+        <v/>
+      </c>
+      <c r="F106">
+        <f>ROUND(D106*0.95,0)</f>
+        <v/>
+      </c>
+      <c r="G106">
+        <f>ROUND(F106-C106,0)</f>
+        <v/>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>revenant</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="6" t="inlineStr">
+        <is>
+          <t>Condition Quickness Evoker Specialized Elements</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>condition</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>0</v>
+      </c>
+      <c r="D107" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107">
+        <f>ROUND(C107/D107*100,2)</f>
+        <v/>
+      </c>
+      <c r="F107">
+        <f>ROUND(D107*0.95,0)</f>
+        <v/>
+      </c>
+      <c r="G107">
+        <f>ROUND(F107-C107,0)</f>
+        <v/>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
           <t>elementalist</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G104"/>
+  <autoFilter ref="A1:G107"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4162,7 +4267,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="13" customWidth="1" min="8" max="8"/>
@@ -4458,7 +4563,7 @@
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>Power Alacrity Luminary Longbow Greatsword</t>
+          <t>Power Alacrity Luminary Spear Greatsword</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4470,7 +4575,7 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>36532</v>
+        <v>37132</v>
       </c>
       <c r="E9">
         <f>ROUND(C9/D9*100,2)</f>
@@ -4493,7 +4598,7 @@
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>Power Alacrity Luminary Spear Greatsword</t>
+          <t>Power Alacrity Luminary Longbow Greatsword</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4505,7 +4610,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>36146</v>
+        <v>36532</v>
       </c>
       <c r="E10">
         <f>ROUND(C10/D10*100,2)</f>
@@ -4946,9 +5051,9 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>Power Alacrity Tempest Hammer</t>
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>Power Alacrity Mechanist Two Kits Sword Pistol</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4960,7 +5065,7 @@
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>34518</v>
+        <v>34572</v>
       </c>
       <c r="E23">
         <f>ROUND(C23/D23*100,2)</f>
@@ -4976,26 +5081,26 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>elementalist</t>
+          <t>engineer</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Condition Alacrity Tempest Fire Only Scepter Focus</t>
+          <t>Power Alacrity Tempest Hammer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>condition</t>
+          <t>power</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>34438</v>
+        <v>34518</v>
       </c>
       <c r="E24">
         <f>ROUND(C24/D24*100,2)</f>
@@ -5016,21 +5121,21 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>Power Alacrity Mechanist Two Kits Sword Pistol</t>
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Condition Alacrity Tempest Fire Only Scepter Focus</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>condition</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>34410</v>
+        <v>34438</v>
       </c>
       <c r="E25">
         <f>ROUND(C25/D25*100,2)</f>
@@ -5046,14 +5151,14 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>engineer</t>
+          <t>elementalist</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>Power Alacrity Evoker Scepter Dagger</t>
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>Power Alacrity Mechanist Sword Pistol</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5065,7 +5170,7 @@
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>34372</v>
+        <v>34414</v>
       </c>
       <c r="E26">
         <f>ROUND(C26/D26*100,2)</f>
@@ -5081,26 +5186,26 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>elementalist</t>
+          <t>engineer</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>Condition Alacrity Tempest Pistol Warhorn</t>
+          <t>Power Alacrity Evoker Scepter Dagger</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>condition</t>
+          <t>power</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>34126</v>
+        <v>34372</v>
       </c>
       <c r="E27">
         <f>ROUND(C27/D27*100,2)</f>
@@ -5121,9 +5226,9 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>Condition Alacrity Specter Scepter Dagger Dagger</t>
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Condition Alacrity Tempest Pistol Warhorn</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5135,7 +5240,7 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>33853</v>
+        <v>34126</v>
       </c>
       <c r="E28">
         <f>ROUND(C28/D28*100,2)</f>
@@ -5151,14 +5256,14 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>thief</t>
+          <t>elementalist</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>Condition Alacrity Tempest Scepter Warhorn</t>
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Condition Alacrity Specter Scepter Dagger Dagger</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5170,7 +5275,7 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>33647</v>
+        <v>33853</v>
       </c>
       <c r="E29">
         <f>ROUND(C29/D29*100,2)</f>
@@ -5186,14 +5291,14 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>elementalist</t>
+          <t>thief</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>Condition Alacrity Specter Scepter Pistol Scepter Pistol</t>
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Condition Alacrity Tempest Scepter Warhorn</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5205,7 +5310,7 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>33548</v>
+        <v>33647</v>
       </c>
       <c r="E30">
         <f>ROUND(C30/D30*100,2)</f>
@@ -5221,26 +5326,26 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>thief</t>
+          <t>elementalist</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="inlineStr">
-        <is>
-          <t>Power Alacrity Renegade Greatsword Sword Sword</t>
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Condition Alacrity Specter Scepter Pistol Scepter Pistol</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>condition</t>
         </is>
       </c>
       <c r="C31" t="n">
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>33459</v>
+        <v>33548</v>
       </c>
       <c r="E31">
         <f>ROUND(C31/D31*100,2)</f>
@@ -5256,26 +5361,26 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>revenant</t>
+          <t>thief</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>Condition Alacrity Renegade Spear Only</t>
+          <t>Power Alacrity Renegade Greatsword Sword Sword</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>condition</t>
+          <t>power</t>
         </is>
       </c>
       <c r="C32" t="n">
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>33300</v>
+        <v>33459</v>
       </c>
       <c r="E32">
         <f>ROUND(C32/D32*100,2)</f>
@@ -5296,21 +5401,21 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>Power Alacrity Paragon Sword Axe Dagger Mace</t>
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>Condition Alacrity Renegade Spear Only</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>condition</t>
         </is>
       </c>
       <c r="C33" t="n">
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>33015</v>
+        <v>33300</v>
       </c>
       <c r="E33">
         <f>ROUND(C33/D33*100,2)</f>
@@ -5326,14 +5431,14 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>warrior</t>
+          <t>revenant</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="10" t="inlineStr">
-        <is>
-          <t>Power Alacrity Renegade Staff Sword Sword</t>
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Power Alacrity Paragon Sword Axe Dagger Mace</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -5345,7 +5450,7 @@
         <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>32850</v>
+        <v>33015</v>
       </c>
       <c r="E34">
         <f>ROUND(C34/D34*100,2)</f>
@@ -5361,14 +5466,14 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>revenant</t>
+          <t>warrior</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>Power Alacrity Tempest Sword Dagger</t>
+      <c r="A35" s="10" t="inlineStr">
+        <is>
+          <t>Power Alacrity Renegade Staff Sword Sword</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -5380,7 +5485,7 @@
         <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>32500</v>
+        <v>32850</v>
       </c>
       <c r="E35">
         <f>ROUND(C35/D35*100,2)</f>
@@ -5396,26 +5501,26 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>elementalist</t>
+          <t>revenant</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="8" t="inlineStr">
-        <is>
-          <t>Condition Alacrity Scourge Scepter Torch Pistol</t>
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>Power Alacrity Tempest Sword Dagger</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>condition</t>
+          <t>power</t>
         </is>
       </c>
       <c r="C36" t="n">
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>32404</v>
+        <v>32500</v>
       </c>
       <c r="E36">
         <f>ROUND(C36/D36*100,2)</f>
@@ -5431,26 +5536,26 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>necromancer</t>
+          <t>elementalist</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>Power Boon Chronomancer Greatsword Dagger Focus</t>
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>Condition Alacrity Scourge Scepter Torch Pistol</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>condition</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>31888</v>
+        <v>32404</v>
       </c>
       <c r="E37">
         <f>ROUND(C37/D37*100,2)</f>
@@ -5466,14 +5571,14 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>mesmer</t>
+          <t>necromancer</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="11" t="inlineStr">
-        <is>
-          <t>Power Alacrity Willbender Greatsword Sword Focus</t>
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>Power Alacrity Mechanist Rifle</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -5485,7 +5590,7 @@
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>31884</v>
+        <v>32248</v>
       </c>
       <c r="E38">
         <f>ROUND(C38/D38*100,2)</f>
@@ -5501,14 +5606,14 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>guardian</t>
+          <t>engineer</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="11" t="inlineStr">
-        <is>
-          <t>Power Alacrity Willbender Spear Greatsword</t>
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>Power Boon Chronomancer Greatsword Dagger Focus</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5520,7 +5625,7 @@
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>31579</v>
+        <v>31888</v>
       </c>
       <c r="E39">
         <f>ROUND(C39/D39*100,2)</f>
@@ -5536,26 +5641,26 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>guardian</t>
+          <t>mesmer</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="11" t="inlineStr">
         <is>
-          <t>Condition Alacrity Willbender Pistol Pistol Axe Torch</t>
+          <t>Power Alacrity Willbender Greatsword Sword Focus</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>condition</t>
+          <t>power</t>
         </is>
       </c>
       <c r="C40" t="n">
         <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>31223</v>
+        <v>31884</v>
       </c>
       <c r="E40">
         <f>ROUND(C40/D40*100,2)</f>
@@ -5576,9 +5681,9 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="7" t="inlineStr">
-        <is>
-          <t>Power Alacrity Mechanist Rifle</t>
+      <c r="A41" s="11" t="inlineStr">
+        <is>
+          <t>Power Alacrity Willbender Spear Greatsword</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5590,7 +5695,7 @@
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>31193</v>
+        <v>31579</v>
       </c>
       <c r="E41">
         <f>ROUND(C41/D41*100,2)</f>
@@ -5606,14 +5711,14 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>engineer</t>
+          <t>guardian</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="7" t="inlineStr">
-        <is>
-          <t>Condition Alacrity Mechanist One Kit Pistol Pistol</t>
+      <c r="A42" s="11" t="inlineStr">
+        <is>
+          <t>Condition Alacrity Willbender Pistol Pistol Axe Torch</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5625,7 +5730,7 @@
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>30772</v>
+        <v>31223</v>
       </c>
       <c r="E42">
         <f>ROUND(C42/D42*100,2)</f>
@@ -5641,26 +5746,26 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>engineer</t>
+          <t>guardian</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t>Celestial Alacrity Tempest Scepter Warhorn</t>
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>Condition Alacrity Mechanist One Kit Pistol Pistol</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>condition</t>
         </is>
       </c>
       <c r="C43" t="n">
         <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>21250</v>
+        <v>30772</v>
       </c>
       <c r="E43">
         <f>ROUND(C43/D43*100,2)</f>
@@ -5676,12 +5781,47 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
+          <t>engineer</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>Celestial Alacrity Tempest Scepter Warhorn</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>power</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>21250</v>
+      </c>
+      <c r="E44">
+        <f>ROUND(C44/D44*100,2)</f>
+        <v/>
+      </c>
+      <c r="F44">
+        <f>ROUND(D44*0.95,0)</f>
+        <v/>
+      </c>
+      <c r="G44">
+        <f>ROUND(F44-C44,0)</f>
+        <v/>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
           <t>elementalist</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G43"/>
+  <autoFilter ref="A1:G44"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6021,9 +6161,9 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>Power Boon Chronomancer Spear Dagger Sword</t>
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>Power Quickness Conduit Staff Sword Sword</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -6035,7 +6175,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>35435</v>
+        <v>35553</v>
       </c>
       <c r="E10">
         <f>ROUND(C10/D10*100,2)</f>
@@ -6051,26 +6191,26 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>mesmer</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>Condition Quickness Firebrand Axe Torch Pistol Pistol</t>
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Power Boon Chronomancer Spear Dagger Sword</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>condition</t>
+          <t>power</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>35420</v>
+        <v>35435</v>
       </c>
       <c r="E11">
         <f>ROUND(C11/D11*100,2)</f>
@@ -6086,26 +6226,26 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>guardian</t>
+          <t>mesmer</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Power Quickness Galeshot Longbow Axe Axe</t>
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>Condition Quickness Firebrand Axe Torch Pistol Pistol</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>condition</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>35330</v>
+        <v>35420</v>
       </c>
       <c r="E12">
         <f>ROUND(C12/D12*100,2)</f>
@@ -6121,14 +6261,14 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>ranger</t>
+          <t>guardian</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Power Quickness Untamed Hammer Sword Axe</t>
+          <t>Power Quickness Galeshot Longbow Axe Axe</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -6140,7 +6280,7 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>35258</v>
+        <v>35330</v>
       </c>
       <c r="E13">
         <f>ROUND(C13/D13*100,2)</f>
@@ -6161,9 +6301,9 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>Power Quickness Berserker Greatsword Axe Axe</t>
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Power Quickness Untamed Hammer Sword Axe</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6175,7 +6315,7 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>35168</v>
+        <v>35258</v>
       </c>
       <c r="E14">
         <f>ROUND(C14/D14*100,2)</f>
@@ -6191,14 +6331,14 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>warrior</t>
+          <t>ranger</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Power Quickness Berserker Spear Axe Axe</t>
+          <t>Power Quickness Berserker Greatsword Axe Axe</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6210,7 +6350,7 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>35096</v>
+        <v>35168</v>
       </c>
       <c r="E15">
         <f>ROUND(C15/D15*100,2)</f>
@@ -6231,9 +6371,9 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>Power Quickness Catalyst Scepter Dagger</t>
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Power Quickness Berserker Spear Axe Axe</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -6245,7 +6385,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>35068</v>
+        <v>35096</v>
       </c>
       <c r="E16">
         <f>ROUND(C16/D16*100,2)</f>
@@ -6261,26 +6401,26 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>elementalist</t>
+          <t>warrior</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>Condition Quickness Untamed Axe Dagger Dagger Torch</t>
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Power Quickness Catalyst Scepter Dagger</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>condition</t>
+          <t>power</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>35006</v>
+        <v>35068</v>
       </c>
       <c r="E17">
         <f>ROUND(C17/D17*100,2)</f>
@@ -6296,26 +6436,26 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>ranger</t>
+          <t>elementalist</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>Power Quickness Conduit Greatsword Sword Sword</t>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Condition Quickness Untamed Axe Dagger Dagger Torch</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>condition</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>34871</v>
+        <v>35006</v>
       </c>
       <c r="E18">
         <f>ROUND(C18/D18*100,2)</f>
@@ -6331,14 +6471,14 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>ranger</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>Power Boon Chronomancer Greatsword Spear</t>
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>Power Quickness Conduit Greatsword Sword Sword</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -6350,7 +6490,7 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>34826</v>
+        <v>34871</v>
       </c>
       <c r="E19">
         <f>ROUND(C19/D19*100,2)</f>
@@ -6366,14 +6506,14 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>mesmer</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>Power Boon Chronomancer Greatsword Dagger Sword</t>
+          <t>Power Boon Chronomancer Greatsword Spear</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -6385,7 +6525,7 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>34824</v>
+        <v>34826</v>
       </c>
       <c r="E20">
         <f>ROUND(C20/D20*100,2)</f>
@@ -6406,21 +6546,21 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>Condition Quickness Scrapper Spear</t>
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Power Boon Chronomancer Greatsword Dagger Sword</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>condition</t>
+          <t>power</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>34765</v>
+        <v>34824</v>
       </c>
       <c r="E21">
         <f>ROUND(C21/D21*100,2)</f>
@@ -6436,14 +6576,14 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>engineer</t>
+          <t>mesmer</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>Condition Boon Chronomancer Staff Scepter Torch</t>
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>Condition Quickness Scrapper Spear</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -6455,7 +6595,7 @@
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>34701</v>
+        <v>34765</v>
       </c>
       <c r="E22">
         <f>ROUND(C22/D22*100,2)</f>
@@ -6471,26 +6611,26 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>mesmer</t>
+          <t>engineer</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>Power Quickness Conduit Staff Sword Sword</t>
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Condition Boon Chronomancer Staff Scepter Torch</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>condition</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>34511</v>
+        <v>34701</v>
       </c>
       <c r="E23">
         <f>ROUND(C23/D23*100,2)</f>
@@ -6506,7 +6646,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>mesmer</t>
         </is>
       </c>
     </row>
@@ -6931,21 +7071,21 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>Power Boon Chronomancer Greatsword Dagger Focus</t>
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t>Condition Quickness Herald Shortbow Mace Axe</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>condition</t>
         </is>
       </c>
       <c r="C36" t="n">
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>31888</v>
+        <v>32014</v>
       </c>
       <c r="E36">
         <f>ROUND(C36/D36*100,2)</f>
@@ -6961,26 +7101,26 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>mesmer</t>
+          <t>revenant</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="10" t="inlineStr">
-        <is>
-          <t>Condition Quickness Herald Spear Mace Axe</t>
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>Power Boon Chronomancer Greatsword Dagger Focus</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>condition</t>
+          <t>power</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>31339</v>
+        <v>31888</v>
       </c>
       <c r="E37">
         <f>ROUND(C37/D37*100,2)</f>
@@ -6996,14 +7136,14 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>revenant</t>
+          <t>mesmer</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>Condition Quickness Herald Shortbow Mace Axe</t>
+          <t>Condition Quickness Herald Spear Mace Axe</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -7015,7 +7155,7 @@
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>31289</v>
+        <v>31339</v>
       </c>
       <c r="E38">
         <f>ROUND(C38/D38*100,2)</f>
